--- a/diseases/d090/2010-2014.xlsx
+++ b/diseases/d090/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6842,6 +7047,11 @@
       <c r="S43" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">

--- a/diseases/d090/2010-2014.xlsx
+++ b/diseases/d090/2010-2014.xlsx
@@ -6924,11 +6924,6 @@
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
@@ -6946,12 +6941,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6961,11 +6951,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7031,17 +7016,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>US-NH</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>New Hampshire, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7075,102 +7060,24 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:US-NH:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>1</v>
-      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7178,12 +7085,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7193,11 +7095,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7268,12 +7165,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7307,13 +7204,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7412,12 +7309,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7442,7 +7339,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2014-07-12</t>
+          <t>2014-07-19</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7451,13 +7348,19 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>28</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.008665635247684296</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7471,7 +7374,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
@@ -7499,32 +7402,32 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7459,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7595,19 +7498,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.008665635247684296</v>
+        <v>1</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7621,7 +7518,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
@@ -7649,32 +7546,32 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7603,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7850,12 +7747,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7889,13 +7786,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7994,12 +7891,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-NJ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>New Jersey, United States</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8033,13 +7930,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -8138,12 +8035,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>US-NJ</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>New Jersey, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8177,13 +8074,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -8282,12 +8179,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8321,13 +8218,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -8426,12 +8323,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8456,7 +8353,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2014-07-19</t>
+          <t>2014-07-26</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -8465,13 +8362,19 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>53</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.01640280957597385</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8485,7 +8388,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
@@ -8513,32 +8416,32 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -8570,12 +8473,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8609,19 +8512,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.01640280957597385</v>
+        <v>2</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8635,7 +8532,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
@@ -8663,32 +8560,32 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8617,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8759,13 +8656,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8864,12 +8761,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-NH</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>New Hampshire, United States</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8903,13 +8800,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -9008,12 +8905,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>US-NH</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>New Hampshire, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9047,18 +8944,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>28</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -9077,12 +8969,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -9092,11 +8979,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9162,17 +9044,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>US-NH</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>New Hampshire, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9206,102 +9088,24 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:US-NH:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9309,12 +9113,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -9324,11 +9123,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9399,12 +9193,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9429,22 +9223,28 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="O60" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="P60" t="n">
-        <v>28</v>
+        <v>67</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.020735627199816</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -9458,7 +9258,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
@@ -9486,32 +9286,32 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9543,12 +9343,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9573,22 +9373,22 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="P61" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -9687,12 +9487,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9726,19 +9526,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="O62" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.020735627199816</v>
+        <v>16</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -9752,7 +9546,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
@@ -9780,32 +9574,32 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9631,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9867,7 +9661,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -9876,13 +9670,19 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O63" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P63" t="n">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.01423640076405277</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -9896,7 +9696,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
@@ -9924,32 +9724,32 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9781,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10011,7 +9811,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -10020,13 +9820,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -10125,12 +9925,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10164,19 +9964,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="O65" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P65" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0.01423640076405277</v>
+        <v>34</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -10190,7 +9984,7 @@
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
@@ -10218,32 +10012,32 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10069,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10314,13 +10108,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -10419,12 +10213,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10449,7 +10243,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -10458,13 +10252,19 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="O67" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P67" t="n">
-        <v>34</v>
+        <v>49</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.01516486168344752</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -10478,7 +10278,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
@@ -10506,32 +10306,32 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10363,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10593,7 +10393,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-08-16</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -10602,13 +10402,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -10707,12 +10507,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10746,19 +10546,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O69" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="P69" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.01516486168344752</v>
+        <v>35</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -10772,7 +10566,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
@@ -10800,32 +10594,32 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10651,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10896,13 +10690,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -11001,12 +10795,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11031,7 +10825,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2014-08-16</t>
+          <t>2014-08-23</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -11040,13 +10834,19 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="O71" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="P71" t="n">
-        <v>35</v>
+        <v>59</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.01825973141476334</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -11060,7 +10860,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
@@ -11088,32 +10888,32 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11145,12 +10945,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11175,7 +10975,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2014-08-16</t>
+          <t>2014-08-23</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -11184,13 +10984,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -11289,12 +11089,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11328,19 +11128,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.01825973141476334</v>
+        <v>2</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -11354,7 +11148,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
@@ -11382,32 +11176,32 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11439,12 +11233,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11478,13 +11272,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -11583,12 +11377,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11622,13 +11416,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -11727,12 +11521,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11757,7 +11551,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -11766,13 +11560,19 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="O76" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="P76" t="n">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.006189739462631641</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -11786,7 +11586,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
@@ -11814,32 +11614,32 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11671,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11901,7 +11701,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -11910,13 +11710,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -12015,12 +11815,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12054,19 +11854,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.006189739462631641</v>
+        <v>16</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -12080,7 +11874,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
@@ -12108,32 +11902,32 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12165,12 +11959,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12309,12 +12103,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-VT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Vermont, United States</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12348,13 +12142,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -12453,12 +12247,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12483,22 +12277,28 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="P81" t="n">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.0120699919521317</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -12512,7 +12312,7 @@
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
@@ -12540,32 +12340,32 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12597,12 +12397,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>US-VT</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Vermont, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12627,22 +12427,22 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2014-09-06</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -12741,12 +12541,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12780,19 +12580,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.0120699919521317</v>
+        <v>8</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -12806,7 +12600,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
@@ -12834,32 +12628,32 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12685,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12921,7 +12715,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
+          <t>2014-09-13</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -12930,13 +12724,19 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O84" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P84" t="n">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.005880252489500059</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -12950,7 +12750,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
@@ -12978,32 +12778,32 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13035,12 +12835,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13065,7 +12865,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2014-09-06</t>
+          <t>2014-09-13</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -13074,13 +12874,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -13209,7 +13009,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2014-09-13</t>
+          <t>2014-09-20</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13218,19 +13018,19 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="O86" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="P86" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.005880252489500059</v>
+        <v>0.01114153103273695</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -13329,12 +13129,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13359,7 +13159,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2014-09-13</t>
+          <t>2014-09-20</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -13368,13 +13168,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -13473,12 +13273,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13512,19 +13312,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="O88" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="P88" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.01114153103273695</v>
+        <v>20</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -13538,7 +13332,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
@@ -13566,32 +13360,32 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13623,12 +13417,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13662,13 +13456,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -13767,12 +13561,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13797,7 +13591,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2014-09-20</t>
+          <t>2014-09-27</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -13806,13 +13600,19 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O90" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P90" t="n">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.004951791570105312</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -13826,7 +13626,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
@@ -13854,32 +13654,32 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13911,12 +13711,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13941,7 +13741,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2014-09-20</t>
+          <t>2014-09-27</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -13950,13 +13750,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -14055,12 +13855,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14094,19 +13894,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.004951791570105312</v>
+        <v>1</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -14120,7 +13914,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
@@ -14148,32 +13942,32 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14205,12 +13999,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US-NH</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>New Hampshire, United States</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14349,12 +14143,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14388,13 +14182,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P94" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
@@ -14493,12 +14287,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>US-NH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>New Hampshire, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14523,27 +14317,28 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2014-09-27</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="P95" t="n">
-        <v>1</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.008356148274552715</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -14557,17 +14352,12 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -14578,11 +14368,6 @@
       <c r="AT95" t="n">
         <v>1</v>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14595,32 +14380,32 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -14647,17 +14432,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>US-NH</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>New Hampshire, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14682,111 +14467,33 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2014-09-27</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>country:US-NH:national</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN96" t="b">
-        <v>1</v>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14794,12 +14501,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -14809,11 +14511,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14884,12 +14581,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14914,22 +14611,22 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2014-09-27</t>
+          <t>2014-10-04</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-10</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -15058,7 +14755,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15067,19 +14764,19 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.008356148274552715</v>
+        <v>0.001237947892526328</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -15208,7 +14905,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2014-10-11</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -15217,13 +14914,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -15322,12 +15019,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15352,7 +15049,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2014-10-04</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15361,13 +15058,19 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P100" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.001856921838789492</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -15381,7 +15084,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
@@ -15409,32 +15112,32 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15466,12 +15169,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15496,7 +15199,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2014-10-11</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15513,12 +15216,6 @@
       <c r="P101" t="n">
         <v>4</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.001237947892526328</v>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
@@ -15531,7 +15228,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
@@ -15559,32 +15256,32 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15616,12 +15313,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15646,7 +15343,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2014-10-11</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15655,13 +15352,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15790,7 +15487,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2014-10-18</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -15799,19 +15496,19 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.001856921838789492</v>
+        <v>0.002166408811921074</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -15910,12 +15607,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15940,7 +15637,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2014-10-18</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -15949,13 +15646,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
@@ -16054,12 +15751,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16084,7 +15781,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2014-10-18</t>
+          <t>2014-10-25</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -16093,13 +15790,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -16198,12 +15895,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16237,19 +15934,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P106" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0.002166408811921074</v>
+        <v>3</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -16263,7 +15954,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
@@ -16291,32 +15982,32 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16348,12 +16039,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16378,22 +16069,28 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P107" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.002166408811921074</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -16407,7 +16104,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
@@ -16435,32 +16132,32 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16522,22 +16219,22 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -16666,22 +16363,22 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2014-10-25</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-11</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -16810,7 +16507,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -16930,12 +16627,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16960,7 +16657,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -17074,12 +16771,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US-RI</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhode Island, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17104,7 +16801,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-11-08</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -17248,7 +16945,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2014-11-08</t>
+          <t>2014-11-15</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -17257,19 +16954,19 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O113" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P113" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.002166408811921074</v>
+        <v>0.003713843677578984</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -17368,12 +17065,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17398,7 +17095,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2014-11-08</t>
+          <t>2014-11-15</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -17407,13 +17104,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -17512,12 +17209,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17542,7 +17239,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2014-11-08</t>
+          <t>2014-11-22</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -17551,13 +17248,19 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P115" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.00154743486565791</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -17571,7 +17274,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
@@ -17599,32 +17302,32 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17656,12 +17359,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17686,7 +17389,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2014-11-15</t>
+          <t>2014-11-22</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -17695,19 +17398,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.003713843677578984</v>
+        <v>1</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -17721,7 +17418,7 @@
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
@@ -17749,32 +17446,32 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17533,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2014-11-15</t>
+          <t>2014-11-22</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -17845,13 +17542,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O117" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P117" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -17980,7 +17677,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2014-11-22</t>
+          <t>2014-11-29</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -17989,19 +17686,19 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.00154743486565791</v>
+        <v>0.002166408811921074</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -18100,12 +17797,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18130,7 +17827,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2014-11-22</t>
+          <t>2014-11-29</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -18244,12 +17941,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-ME</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Maine, United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -18274,7 +17971,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2014-11-22</t>
+          <t>2014-11-29</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -18283,13 +17980,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -18388,12 +18085,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18427,19 +18124,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P121" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.002166408811921074</v>
+        <v>5</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -18453,7 +18144,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
@@ -18481,32 +18172,32 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18538,12 +18229,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -18568,12 +18259,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
+          <t>2014-12-06</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -18585,6 +18276,12 @@
       <c r="P122" t="n">
         <v>1</v>
       </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.000309486973131582</v>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
@@ -18597,7 +18294,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
@@ -18625,32 +18322,32 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18682,12 +18379,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US-ME</t>
+          <t>US-MD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Maine, United States</t>
+          <t>Maryland, United States</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -18712,12 +18409,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
+          <t>2014-12-06</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -18826,12 +18523,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -18856,22 +18553,28 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2014-11-29</t>
+          <t>2014-12-13</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-12</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P124" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.001237947892526328</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -18885,7 +18588,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
@@ -18913,32 +18616,32 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18970,12 +18673,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -19000,7 +18703,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2014-12-06</t>
+          <t>2014-12-13</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -19009,19 +18712,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.000309486973131582</v>
+        <v>3</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -19035,7 +18732,7 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
@@ -19063,32 +18760,32 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19120,12 +18817,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US-MD</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Maryland, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -19150,7 +18847,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2014-12-06</t>
+          <t>2014-12-20</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -19159,13 +18856,19 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P126" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.002475895785052656</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -19179,7 +18882,7 @@
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
@@ -19207,32 +18910,32 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19264,12 +18967,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -19294,7 +18997,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2014-12-13</t>
+          <t>2014-12-20</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -19303,19 +19006,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P127" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.001237947892526328</v>
+        <v>1</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -19329,7 +19026,7 @@
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
@@ -19357,32 +19054,32 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19444,7 +19141,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2014-12-13</t>
+          <t>2014-12-20</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -19453,13 +19150,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -19558,12 +19255,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -19597,19 +19294,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P129" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.002475895785052656</v>
+        <v>5</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -19623,7 +19314,7 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
@@ -19651,32 +19342,32 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19708,12 +19399,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -19738,7 +19429,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2014-12-20</t>
+          <t>2014-12-27</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -19755,6 +19446,12 @@
       <c r="P130" t="n">
         <v>1</v>
       </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.000309486973131582</v>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
@@ -19767,7 +19464,7 @@
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
@@ -19795,32 +19492,32 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19852,12 +19549,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US-RI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>Rhode Island, United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -19882,7 +19579,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2014-12-20</t>
+          <t>2014-12-27</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -19963,444 +19660,6 @@
         </is>
       </c>
       <c r="BC131" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>babesiosis</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>US-RI</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Rhode Island, United States</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>巴贝西虫病</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>2014-12-20</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N132" t="n">
-        <v>5</v>
-      </c>
-      <c r="O132" t="n">
-        <v>5</v>
-      </c>
-      <c r="P132" t="n">
-        <v>5</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AT132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>babesiosis</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>巴贝西虫病</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>2014-12-27</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N133" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.000309486973131582</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AT133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV133" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA133" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB133" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC133" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>babesiosis</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>US-RI</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Rhode Island, United States</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>D090</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Babesiosis</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>巴贝西虫病</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>2014-12-27</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>2014-12</t>
-        </is>
-      </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>1</v>
-      </c>
-      <c r="P134" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>HOLD_US_776dcfa4cceabbafa95092b601d2</t>
-        </is>
-      </c>
-      <c r="AT134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV134" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA134" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB134" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC134" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20532,7 +19791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -20552,7 +19811,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -20562,7 +19821,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
